--- a/artfynd/A 16954-2025 artfynd.xlsx
+++ b/artfynd/A 16954-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124172562</v>
+        <v>124172528</v>
       </c>
       <c r="B2" t="n">
-        <v>57861</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -717,7 +717,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562084</v>
+        <v>562104</v>
       </c>
       <c r="R2" t="n">
-        <v>6407227</v>
+        <v>6407251</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -789,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124172016</v>
+        <v>124172266</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562185</v>
+        <v>562099</v>
       </c>
       <c r="R3" t="n">
-        <v>6407314</v>
+        <v>6407295</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +900,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124172370</v>
+        <v>124172046</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562074</v>
+        <v>562174</v>
       </c>
       <c r="R4" t="n">
-        <v>6407252</v>
+        <v>6407304</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124172400</v>
+        <v>124172327</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,35 +1023,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562048</v>
+        <v>562106</v>
       </c>
       <c r="R5" t="n">
-        <v>6407247</v>
+        <v>6407323</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,7 +1125,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124172454</v>
+        <v>124171931</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1170,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561985</v>
+        <v>562188</v>
       </c>
       <c r="R6" t="n">
-        <v>6407239</v>
+        <v>6407299</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124172266</v>
+        <v>124172498</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,35 +1248,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1281,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562099</v>
+        <v>562127</v>
       </c>
       <c r="R7" t="n">
-        <v>6407295</v>
+        <v>6407212</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,13 +1322,17 @@
           <t>2025-04-17</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Torrträd</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1344,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124172550</v>
+        <v>124172151</v>
       </c>
       <c r="B8" t="n">
-        <v>57861</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,53 +1363,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A  16954, Vrå, Sm</t>
+          <t>A 16954, Vrå, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562129</v>
+        <v>562104</v>
       </c>
       <c r="R8" t="n">
-        <v>6407291</v>
+        <v>6407296</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,6 +1443,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1458,7 +1462,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124171931</v>
+        <v>124172454</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1506,10 +1510,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562188</v>
+        <v>561985</v>
       </c>
       <c r="R9" t="n">
-        <v>6407299</v>
+        <v>6407239</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,10 +1573,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124172528</v>
+        <v>124172016</v>
       </c>
       <c r="B10" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1581,39 +1585,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1621,13 +1621,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562104</v>
+        <v>562185</v>
       </c>
       <c r="R10" t="n">
-        <v>6407251</v>
+        <v>6407314</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1665,6 +1665,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1683,10 +1684,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124171837</v>
+        <v>124172219</v>
       </c>
       <c r="B11" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,35 +1696,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1731,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562199</v>
+        <v>562109</v>
       </c>
       <c r="R11" t="n">
-        <v>6407237</v>
+        <v>6407282</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1769,17 +1770,13 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Låga</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1798,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124172481</v>
+        <v>124172562</v>
       </c>
       <c r="B12" t="n">
-        <v>98079</v>
+        <v>57861</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1810,35 +1807,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1846,13 +1847,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562037</v>
+        <v>562084</v>
       </c>
       <c r="R12" t="n">
-        <v>6407226</v>
+        <v>6407227</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1890,7 +1891,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1909,10 +1909,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124172219</v>
+        <v>124171893</v>
       </c>
       <c r="B13" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1921,35 +1921,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1957,13 +1961,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562109</v>
+        <v>562174</v>
       </c>
       <c r="R13" t="n">
-        <v>6407282</v>
+        <v>6407246</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1995,13 +1999,17 @@
           <t>2025-04-17</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Även sång</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2020,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124172151</v>
+        <v>124171837</v>
       </c>
       <c r="B14" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2032,35 +2040,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2068,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562104</v>
+        <v>562199</v>
       </c>
       <c r="R14" t="n">
-        <v>6407296</v>
+        <v>6407237</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2106,13 +2114,17 @@
           <t>2025-04-17</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Låga</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2131,10 +2143,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124172327</v>
+        <v>124172370</v>
       </c>
       <c r="B15" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2143,38 +2155,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2182,10 +2191,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562106</v>
+        <v>562074</v>
       </c>
       <c r="R15" t="n">
-        <v>6407323</v>
+        <v>6407252</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,7 +2254,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124172046</v>
+        <v>124172400</v>
       </c>
       <c r="B16" t="n">
         <v>98079</v>
@@ -2293,10 +2302,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562174</v>
+        <v>562048</v>
       </c>
       <c r="R16" t="n">
-        <v>6407304</v>
+        <v>6407247</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2356,10 +2365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124172498</v>
+        <v>124172481</v>
       </c>
       <c r="B17" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2368,35 +2377,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2404,10 +2413,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562127</v>
+        <v>562037</v>
       </c>
       <c r="R17" t="n">
-        <v>6407212</v>
+        <v>6407226</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2442,17 +2451,13 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Torrträd</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2471,10 +2476,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124171893</v>
+        <v>124172550</v>
       </c>
       <c r="B18" t="n">
-        <v>57644</v>
+        <v>57861</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2483,50 +2488,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A 16954, Vrå, Sm</t>
+          <t>A  16954, Vrå, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562174</v>
+        <v>562129</v>
       </c>
       <c r="R18" t="n">
-        <v>6407246</v>
+        <v>6407291</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2559,11 +2564,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-17</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Även sång</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 16954-2025 artfynd.xlsx
+++ b/artfynd/A 16954-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124172327</v>
+        <v>124172151</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562106</v>
+        <v>562104</v>
       </c>
       <c r="R2" t="n">
-        <v>6407323</v>
+        <v>6407296</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124172498</v>
+        <v>124172400</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,35 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562127</v>
+        <v>562048</v>
       </c>
       <c r="R3" t="n">
-        <v>6407212</v>
+        <v>6407247</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,17 +872,13 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Torrträd</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -904,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124171837</v>
+        <v>124172562</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>57883</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,20 +909,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -937,12 +930,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -952,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562199</v>
+        <v>562084</v>
       </c>
       <c r="R4" t="n">
-        <v>6407237</v>
+        <v>6407227</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,11 +985,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Låga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124172481</v>
+        <v>124172498</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,35 +1023,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1067,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562037</v>
+        <v>562127</v>
       </c>
       <c r="R5" t="n">
-        <v>6407226</v>
+        <v>6407212</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,13 +1097,17 @@
           <t>2025-04-17</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Torrträd</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1130,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124172454</v>
+        <v>124172528</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,35 +1138,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1178,13 +1178,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561985</v>
+        <v>562104</v>
       </c>
       <c r="R6" t="n">
-        <v>6407239</v>
+        <v>6407251</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,7 +1222,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1241,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124172016</v>
+        <v>124172327</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,35 +1252,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1289,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562185</v>
+        <v>562106</v>
       </c>
       <c r="R7" t="n">
-        <v>6407314</v>
+        <v>6407323</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1352,10 +1354,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124171931</v>
+        <v>124171837</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,35 +1366,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1400,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562188</v>
+        <v>562199</v>
       </c>
       <c r="R8" t="n">
-        <v>6407299</v>
+        <v>6407237</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,13 +1440,17 @@
           <t>2025-04-17</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Låga</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1463,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124172550</v>
+        <v>124172016</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,53 +1481,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A  16954, Vrå, Sm</t>
+          <t>A 16954, Vrå, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562129</v>
+        <v>562185</v>
       </c>
       <c r="R9" t="n">
-        <v>6407291</v>
+        <v>6407314</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1559,6 +1561,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1577,7 +1580,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124172046</v>
+        <v>124172454</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1625,10 +1628,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562174</v>
+        <v>561985</v>
       </c>
       <c r="R10" t="n">
-        <v>6407304</v>
+        <v>6407239</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,10 +1691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124172400</v>
+        <v>124171893</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1700,35 +1703,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1736,13 +1743,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562048</v>
+        <v>562174</v>
       </c>
       <c r="R11" t="n">
-        <v>6407247</v>
+        <v>6407246</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1774,13 +1781,17 @@
           <t>2025-04-17</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Även sång</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1799,7 +1810,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124172562</v>
+        <v>124172550</v>
       </c>
       <c r="B12" t="n">
         <v>57883</v>
@@ -1847,14 +1858,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 16954, Vrå, Sm</t>
+          <t>A  16954, Vrå, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562084</v>
+        <v>562129</v>
       </c>
       <c r="R12" t="n">
-        <v>6407227</v>
+        <v>6407291</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1913,7 +1924,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124172219</v>
+        <v>124171931</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1961,10 +1972,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562109</v>
+        <v>562188</v>
       </c>
       <c r="R13" t="n">
-        <v>6407282</v>
+        <v>6407299</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2024,10 +2035,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124171893</v>
+        <v>124172046</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2036,39 +2047,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2079,10 +2086,10 @@
         <v>562174</v>
       </c>
       <c r="R14" t="n">
-        <v>6407246</v>
+        <v>6407304</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2114,17 +2121,13 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Även sång</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2143,7 +2146,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124172370</v>
+        <v>124172219</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2191,10 +2194,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562074</v>
+        <v>562109</v>
       </c>
       <c r="R15" t="n">
-        <v>6407252</v>
+        <v>6407282</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2365,10 +2368,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124172528</v>
+        <v>124172370</v>
       </c>
       <c r="B17" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2377,39 +2380,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2417,13 +2416,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562104</v>
+        <v>562074</v>
       </c>
       <c r="R17" t="n">
-        <v>6407251</v>
+        <v>6407252</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2461,6 +2460,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2479,7 +2479,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124172151</v>
+        <v>124172481</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562104</v>
+        <v>562037</v>
       </c>
       <c r="R18" t="n">
-        <v>6407296</v>
+        <v>6407226</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 16954-2025 artfynd.xlsx
+++ b/artfynd/A 16954-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124172151</v>
+        <v>124172266</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562104</v>
+        <v>562099</v>
       </c>
       <c r="R2" t="n">
-        <v>6407296</v>
+        <v>6407295</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124172400</v>
+        <v>124171931</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562048</v>
+        <v>562188</v>
       </c>
       <c r="R3" t="n">
-        <v>6407247</v>
+        <v>6407299</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124172562</v>
+        <v>124172550</v>
       </c>
       <c r="B4" t="n">
         <v>57883</v>
@@ -945,14 +945,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 16954, Vrå, Sm</t>
+          <t>A  16954, Vrå, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562084</v>
+        <v>562129</v>
       </c>
       <c r="R4" t="n">
-        <v>6407227</v>
+        <v>6407291</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124172498</v>
+        <v>124172151</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,35 +1023,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562127</v>
+        <v>562104</v>
       </c>
       <c r="R5" t="n">
-        <v>6407212</v>
+        <v>6407296</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,17 +1097,13 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Torrträd</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1126,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124172528</v>
+        <v>124172219</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,39 +1134,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1178,13 +1170,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562104</v>
+        <v>562109</v>
       </c>
       <c r="R6" t="n">
-        <v>6407251</v>
+        <v>6407282</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,6 +1214,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1240,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124172327</v>
+        <v>124172528</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,21 +1249,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1278,12 +1271,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1291,13 +1285,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562106</v>
+        <v>562104</v>
       </c>
       <c r="R7" t="n">
-        <v>6407323</v>
+        <v>6407251</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1335,7 +1329,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1354,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124171837</v>
+        <v>124172498</v>
       </c>
       <c r="B8" t="n">
         <v>57529</v>
@@ -1402,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562199</v>
+        <v>562127</v>
       </c>
       <c r="R8" t="n">
-        <v>6407237</v>
+        <v>6407212</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1435,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Låga</t>
+          <t>Torrträd</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,7 +1462,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124172016</v>
+        <v>124172370</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1517,10 +1510,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562185</v>
+        <v>562074</v>
       </c>
       <c r="R9" t="n">
-        <v>6407314</v>
+        <v>6407252</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,7 +1573,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124172454</v>
+        <v>124172400</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1628,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561985</v>
+        <v>562048</v>
       </c>
       <c r="R10" t="n">
-        <v>6407239</v>
+        <v>6407247</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1691,10 +1684,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124171893</v>
+        <v>124172454</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,39 +1696,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1743,13 +1732,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562174</v>
+        <v>561985</v>
       </c>
       <c r="R11" t="n">
-        <v>6407246</v>
+        <v>6407239</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1781,17 +1770,13 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Även sång</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1810,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124172550</v>
+        <v>124172016</v>
       </c>
       <c r="B12" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1822,53 +1807,49 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A  16954, Vrå, Sm</t>
+          <t>A 16954, Vrå, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562129</v>
+        <v>562185</v>
       </c>
       <c r="R12" t="n">
-        <v>6407291</v>
+        <v>6407314</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1906,6 +1887,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1924,10 +1906,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124171931</v>
+        <v>124172327</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1936,35 +1918,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1972,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562188</v>
+        <v>562106</v>
       </c>
       <c r="R13" t="n">
-        <v>6407299</v>
+        <v>6407323</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2035,10 +2020,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124172046</v>
+        <v>124172562</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2047,35 +2032,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2083,13 +2072,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562174</v>
+        <v>562084</v>
       </c>
       <c r="R14" t="n">
-        <v>6407304</v>
+        <v>6407227</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2127,7 +2116,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2146,7 +2134,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124172219</v>
+        <v>124172046</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2194,10 +2182,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562109</v>
+        <v>562174</v>
       </c>
       <c r="R15" t="n">
-        <v>6407282</v>
+        <v>6407304</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2257,7 +2245,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124172266</v>
+        <v>124172481</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2305,10 +2293,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562099</v>
+        <v>562037</v>
       </c>
       <c r="R16" t="n">
-        <v>6407295</v>
+        <v>6407226</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2368,10 +2356,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124172370</v>
+        <v>124171837</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2380,35 +2368,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2416,10 +2404,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562074</v>
+        <v>562199</v>
       </c>
       <c r="R17" t="n">
-        <v>6407252</v>
+        <v>6407237</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,13 +2442,17 @@
           <t>2025-04-17</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Låga</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2479,10 +2471,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124172481</v>
+        <v>124171893</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2491,35 +2483,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2527,13 +2523,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562037</v>
+        <v>562174</v>
       </c>
       <c r="R18" t="n">
-        <v>6407226</v>
+        <v>6407246</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2565,13 +2561,17 @@
           <t>2025-04-17</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Även sång</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16954-2025 artfynd.xlsx
+++ b/artfynd/A 16954-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124172266</v>
+        <v>124171931</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562099</v>
+        <v>562188</v>
       </c>
       <c r="R2" t="n">
-        <v>6407295</v>
+        <v>6407299</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124171931</v>
+        <v>124172481</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562188</v>
+        <v>562037</v>
       </c>
       <c r="R3" t="n">
-        <v>6407299</v>
+        <v>6407226</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124172550</v>
+        <v>124172266</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,53 +909,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A  16954, Vrå, Sm</t>
+          <t>A 16954, Vrå, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562129</v>
+        <v>562099</v>
       </c>
       <c r="R4" t="n">
-        <v>6407291</v>
+        <v>6407295</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,6 +989,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1011,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124172151</v>
+        <v>124171837</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,35 +1020,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562104</v>
+        <v>562199</v>
       </c>
       <c r="R5" t="n">
-        <v>6407296</v>
+        <v>6407237</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,13 +1094,17 @@
           <t>2025-04-17</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Låga</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1122,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124172219</v>
+        <v>124172046</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1170,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562109</v>
+        <v>562174</v>
       </c>
       <c r="R6" t="n">
-        <v>6407282</v>
+        <v>6407304</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124172528</v>
+        <v>124172454</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,39 +1246,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1285,13 +1282,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562104</v>
+        <v>561985</v>
       </c>
       <c r="R7" t="n">
-        <v>6407251</v>
+        <v>6407239</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1329,6 +1326,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1347,7 +1345,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124172498</v>
+        <v>124172528</v>
       </c>
       <c r="B8" t="n">
         <v>57529</v>
@@ -1380,12 +1378,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1395,13 +1397,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562127</v>
+        <v>562104</v>
       </c>
       <c r="R8" t="n">
-        <v>6407212</v>
+        <v>6407251</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1431,11 +1433,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Torrträd</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124172370</v>
+        <v>124172550</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1474,49 +1471,53 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 16954, Vrå, Sm</t>
+          <t>A  16954, Vrå, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562074</v>
+        <v>562129</v>
       </c>
       <c r="R9" t="n">
-        <v>6407252</v>
+        <v>6407291</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1554,7 +1555,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1573,7 +1573,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124172400</v>
+        <v>124172219</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562048</v>
+        <v>562109</v>
       </c>
       <c r="R10" t="n">
-        <v>6407247</v>
+        <v>6407282</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,7 +1684,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124172454</v>
+        <v>124172370</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561985</v>
+        <v>562074</v>
       </c>
       <c r="R11" t="n">
-        <v>6407239</v>
+        <v>6407252</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124172016</v>
+        <v>124172327</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,35 +1807,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1843,10 +1846,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562185</v>
+        <v>562106</v>
       </c>
       <c r="R12" t="n">
-        <v>6407314</v>
+        <v>6407323</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1906,10 +1909,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124172327</v>
+        <v>124172400</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1918,38 +1921,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562106</v>
+        <v>562048</v>
       </c>
       <c r="R13" t="n">
-        <v>6407323</v>
+        <v>6407247</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,10 +2020,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124172562</v>
+        <v>124172151</v>
       </c>
       <c r="B14" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2032,39 +2032,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2072,13 +2068,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562084</v>
+        <v>562104</v>
       </c>
       <c r="R14" t="n">
-        <v>6407227</v>
+        <v>6407296</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2116,6 +2112,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2134,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124172046</v>
+        <v>124171893</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2146,35 +2143,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2185,10 +2186,10 @@
         <v>562174</v>
       </c>
       <c r="R15" t="n">
-        <v>6407304</v>
+        <v>6407246</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2220,13 +2221,17 @@
           <t>2025-04-17</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Även sång</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2245,7 +2250,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124172481</v>
+        <v>124172016</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2293,10 +2298,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562037</v>
+        <v>562185</v>
       </c>
       <c r="R16" t="n">
-        <v>6407226</v>
+        <v>6407314</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2356,7 +2361,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124171837</v>
+        <v>124172498</v>
       </c>
       <c r="B17" t="n">
         <v>57529</v>
@@ -2404,10 +2409,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562199</v>
+        <v>562127</v>
       </c>
       <c r="R17" t="n">
-        <v>6407237</v>
+        <v>6407212</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2444,7 +2449,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Låga</t>
+          <t>Torrträd</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2471,10 +2476,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124171893</v>
+        <v>124172562</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>57883</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2483,37 +2488,37 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2523,10 +2528,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562174</v>
+        <v>562084</v>
       </c>
       <c r="R18" t="n">
-        <v>6407246</v>
+        <v>6407227</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2559,11 +2564,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-17</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Även sång</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 16954-2025 artfynd.xlsx
+++ b/artfynd/A 16954-2025 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124172481</v>
+        <v>124172528</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +798,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562037</v>
+        <v>562104</v>
       </c>
       <c r="R3" t="n">
-        <v>6407226</v>
+        <v>6407251</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,7 +882,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124172266</v>
+        <v>124172327</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,35 +912,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562099</v>
+        <v>562106</v>
       </c>
       <c r="R4" t="n">
-        <v>6407295</v>
+        <v>6407323</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124171837</v>
+        <v>124172016</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,35 +1026,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1056,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562199</v>
+        <v>562185</v>
       </c>
       <c r="R5" t="n">
-        <v>6407237</v>
+        <v>6407314</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,17 +1100,13 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Låga</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1123,7 +1125,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124172046</v>
+        <v>124172266</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1171,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562174</v>
+        <v>562099</v>
       </c>
       <c r="R6" t="n">
-        <v>6407304</v>
+        <v>6407295</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,7 +1236,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124172454</v>
+        <v>124172400</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1282,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561985</v>
+        <v>562048</v>
       </c>
       <c r="R7" t="n">
-        <v>6407239</v>
+        <v>6407247</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124172528</v>
+        <v>124171893</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>57666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1361,33 +1363,33 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1397,10 +1399,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562104</v>
+        <v>562174</v>
       </c>
       <c r="R8" t="n">
-        <v>6407251</v>
+        <v>6407246</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1433,6 +1435,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Även sång</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1573,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124172219</v>
+        <v>124172562</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1585,35 +1592,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1621,13 +1632,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562109</v>
+        <v>562084</v>
       </c>
       <c r="R10" t="n">
-        <v>6407282</v>
+        <v>6407227</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1665,7 +1676,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1684,7 +1694,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124172370</v>
+        <v>124172454</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1732,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562074</v>
+        <v>561985</v>
       </c>
       <c r="R11" t="n">
-        <v>6407252</v>
+        <v>6407239</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124172327</v>
+        <v>124172498</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,34 +1821,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1846,10 +1853,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562106</v>
+        <v>562127</v>
       </c>
       <c r="R12" t="n">
-        <v>6407323</v>
+        <v>6407212</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1884,13 +1891,17 @@
           <t>2025-04-17</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Torrträd</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1909,10 +1920,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124172400</v>
+        <v>124171837</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1921,35 +1932,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1957,10 +1968,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562048</v>
+        <v>562199</v>
       </c>
       <c r="R13" t="n">
-        <v>6407247</v>
+        <v>6407237</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,13 +2006,17 @@
           <t>2025-04-17</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Låga</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2131,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124171893</v>
+        <v>124172046</v>
       </c>
       <c r="B15" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2143,39 +2158,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2186,10 +2197,10 @@
         <v>562174</v>
       </c>
       <c r="R15" t="n">
-        <v>6407246</v>
+        <v>6407304</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2221,17 +2232,13 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Även sång</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2250,7 +2257,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124172016</v>
+        <v>124172370</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2298,10 +2305,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562185</v>
+        <v>562074</v>
       </c>
       <c r="R16" t="n">
-        <v>6407314</v>
+        <v>6407252</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2361,10 +2368,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124172498</v>
+        <v>124172219</v>
       </c>
       <c r="B17" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2373,35 +2380,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2409,10 +2416,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562127</v>
+        <v>562109</v>
       </c>
       <c r="R17" t="n">
-        <v>6407212</v>
+        <v>6407282</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2447,17 +2454,13 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Torrträd</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2476,10 +2479,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124172562</v>
+        <v>124172481</v>
       </c>
       <c r="B18" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2488,39 +2491,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2528,13 +2527,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562084</v>
+        <v>562037</v>
       </c>
       <c r="R18" t="n">
-        <v>6407227</v>
+        <v>6407226</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2572,6 +2571,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16954-2025 artfynd.xlsx
+++ b/artfynd/A 16954-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124171931</v>
+        <v>124172219</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562188</v>
+        <v>562109</v>
       </c>
       <c r="R2" t="n">
-        <v>6407299</v>
+        <v>6407282</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124172528</v>
+        <v>124172454</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,39 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +834,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562104</v>
+        <v>561985</v>
       </c>
       <c r="R3" t="n">
-        <v>6407251</v>
+        <v>6407239</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,6 +878,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124172327</v>
+        <v>124172528</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -938,12 +935,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562106</v>
+        <v>562104</v>
       </c>
       <c r="R4" t="n">
-        <v>6407323</v>
+        <v>6407251</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,7 +993,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1014,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124172016</v>
+        <v>124172266</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1062,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562185</v>
+        <v>562099</v>
       </c>
       <c r="R5" t="n">
-        <v>6407314</v>
+        <v>6407295</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,7 +1122,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124172266</v>
+        <v>124171931</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1173,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562099</v>
+        <v>562188</v>
       </c>
       <c r="R6" t="n">
-        <v>6407295</v>
+        <v>6407299</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,7 +1233,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124172400</v>
+        <v>124172016</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1284,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562048</v>
+        <v>562185</v>
       </c>
       <c r="R7" t="n">
-        <v>6407247</v>
+        <v>6407314</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124171893</v>
+        <v>124172400</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,39 +1356,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1399,13 +1392,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562174</v>
+        <v>562048</v>
       </c>
       <c r="R8" t="n">
-        <v>6407246</v>
+        <v>6407247</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,17 +1430,13 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Även sång</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1466,7 +1455,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124172550</v>
+        <v>124172562</v>
       </c>
       <c r="B9" t="n">
         <v>57883</v>
@@ -1514,14 +1503,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A  16954, Vrå, Sm</t>
+          <t>A 16954, Vrå, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562129</v>
+        <v>562084</v>
       </c>
       <c r="R9" t="n">
-        <v>6407291</v>
+        <v>6407227</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1580,10 +1569,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124172562</v>
+        <v>124172327</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,25 +1581,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1618,13 +1607,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1632,13 +1620,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562084</v>
+        <v>562106</v>
       </c>
       <c r="R10" t="n">
-        <v>6407227</v>
+        <v>6407323</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1676,6 +1664,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1694,7 +1683,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124172454</v>
+        <v>124172151</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1742,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561985</v>
+        <v>562104</v>
       </c>
       <c r="R11" t="n">
-        <v>6407239</v>
+        <v>6407296</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1805,7 +1794,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124172498</v>
+        <v>124171837</v>
       </c>
       <c r="B12" t="n">
         <v>57529</v>
@@ -1853,10 +1842,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562127</v>
+        <v>562199</v>
       </c>
       <c r="R12" t="n">
-        <v>6407212</v>
+        <v>6407237</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1893,7 +1882,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Torrträd</t>
+          <t>Låga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,10 +1909,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124171837</v>
+        <v>124172046</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1932,35 +1921,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1968,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562199</v>
+        <v>562174</v>
       </c>
       <c r="R13" t="n">
-        <v>6407237</v>
+        <v>6407304</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2006,17 +1995,13 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Låga</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2035,7 +2020,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124172151</v>
+        <v>124172481</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2083,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562104</v>
+        <v>562037</v>
       </c>
       <c r="R14" t="n">
-        <v>6407296</v>
+        <v>6407226</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2146,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124172046</v>
+        <v>124172498</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2158,35 +2143,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2194,10 +2179,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562174</v>
+        <v>562127</v>
       </c>
       <c r="R15" t="n">
-        <v>6407304</v>
+        <v>6407212</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2232,13 +2217,17 @@
           <t>2025-04-17</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Torrträd</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2257,10 +2246,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124172370</v>
+        <v>124172550</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2269,49 +2258,53 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A 16954, Vrå, Sm</t>
+          <t>A  16954, Vrå, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562074</v>
+        <v>562129</v>
       </c>
       <c r="R16" t="n">
-        <v>6407252</v>
+        <v>6407291</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2349,7 +2342,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2368,7 +2360,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124172219</v>
+        <v>124172370</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2416,10 +2408,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562109</v>
+        <v>562074</v>
       </c>
       <c r="R17" t="n">
-        <v>6407282</v>
+        <v>6407252</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2479,10 +2471,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124172481</v>
+        <v>124171893</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2491,35 +2483,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2527,13 +2523,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562037</v>
+        <v>562174</v>
       </c>
       <c r="R18" t="n">
-        <v>6407226</v>
+        <v>6407246</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2565,13 +2561,17 @@
           <t>2025-04-17</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Även sång</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16954-2025 artfynd.xlsx
+++ b/artfynd/A 16954-2025 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124172454</v>
+        <v>124172151</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561985</v>
+        <v>562104</v>
       </c>
       <c r="R3" t="n">
-        <v>6407239</v>
+        <v>6407296</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124172528</v>
+        <v>124172562</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>57883</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,20 +909,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -939,7 +939,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562104</v>
+        <v>562084</v>
       </c>
       <c r="R4" t="n">
-        <v>6407251</v>
+        <v>6407227</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124172266</v>
+        <v>124172370</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562099</v>
+        <v>562074</v>
       </c>
       <c r="R5" t="n">
-        <v>6407295</v>
+        <v>6407252</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124171931</v>
+        <v>124172454</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562188</v>
+        <v>561985</v>
       </c>
       <c r="R6" t="n">
-        <v>6407299</v>
+        <v>6407239</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124172016</v>
+        <v>124172498</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,35 +1245,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562185</v>
+        <v>562127</v>
       </c>
       <c r="R7" t="n">
-        <v>6407314</v>
+        <v>6407212</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,13 +1319,17 @@
           <t>2025-04-17</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Torrträd</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1344,7 +1348,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124172400</v>
+        <v>124171931</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1392,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562048</v>
+        <v>562188</v>
       </c>
       <c r="R8" t="n">
-        <v>6407247</v>
+        <v>6407299</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124172562</v>
+        <v>124172266</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,39 +1471,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562084</v>
+        <v>562099</v>
       </c>
       <c r="R9" t="n">
-        <v>6407227</v>
+        <v>6407295</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1551,6 +1551,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1569,10 +1570,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124172327</v>
+        <v>124172481</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1581,38 +1582,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1620,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562106</v>
+        <v>562037</v>
       </c>
       <c r="R10" t="n">
-        <v>6407323</v>
+        <v>6407226</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,10 +1681,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124172151</v>
+        <v>124172550</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,49 +1693,53 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 16954, Vrå, Sm</t>
+          <t>A  16954, Vrå, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562104</v>
+        <v>562129</v>
       </c>
       <c r="R11" t="n">
-        <v>6407296</v>
+        <v>6407291</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1775,7 +1777,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1794,7 +1795,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124171837</v>
+        <v>124172528</v>
       </c>
       <c r="B12" t="n">
         <v>57529</v>
@@ -1827,12 +1828,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1842,13 +1847,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562199</v>
+        <v>562104</v>
       </c>
       <c r="R12" t="n">
-        <v>6407237</v>
+        <v>6407251</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1878,11 +1883,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-17</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Låga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1909,7 +1909,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124172046</v>
+        <v>124172016</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562174</v>
+        <v>562185</v>
       </c>
       <c r="R13" t="n">
-        <v>6407304</v>
+        <v>6407314</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,7 +2020,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124172481</v>
+        <v>124172046</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562037</v>
+        <v>562174</v>
       </c>
       <c r="R14" t="n">
-        <v>6407226</v>
+        <v>6407304</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124172498</v>
+        <v>124171893</v>
       </c>
       <c r="B15" t="n">
-        <v>57529</v>
+        <v>57666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,29 +2147,33 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2179,13 +2183,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562127</v>
+        <v>562174</v>
       </c>
       <c r="R15" t="n">
-        <v>6407212</v>
+        <v>6407246</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2219,7 +2223,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Torrträd</t>
+          <t>Även sång</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2246,10 +2250,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124172550</v>
+        <v>124171837</v>
       </c>
       <c r="B16" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2258,20 +2262,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2279,32 +2283,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A  16954, Vrå, Sm</t>
+          <t>A 16954, Vrå, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562129</v>
+        <v>562199</v>
       </c>
       <c r="R16" t="n">
-        <v>6407291</v>
+        <v>6407237</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2334,6 +2334,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Låga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2360,7 +2365,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124172370</v>
+        <v>124172400</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2408,10 +2413,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562074</v>
+        <v>562048</v>
       </c>
       <c r="R17" t="n">
-        <v>6407252</v>
+        <v>6407247</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2471,10 +2476,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124171893</v>
+        <v>124172327</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2487,35 +2492,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2523,13 +2527,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562174</v>
+        <v>562106</v>
       </c>
       <c r="R18" t="n">
-        <v>6407246</v>
+        <v>6407323</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2561,17 +2565,13 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Även sång</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16954-2025 artfynd.xlsx
+++ b/artfynd/A 16954-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124172219</v>
+        <v>124171931</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562109</v>
+        <v>562188</v>
       </c>
       <c r="R2" t="n">
-        <v>6407282</v>
+        <v>6407299</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124172151</v>
+        <v>124172016</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562104</v>
+        <v>562185</v>
       </c>
       <c r="R3" t="n">
-        <v>6407296</v>
+        <v>6407314</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124172562</v>
+        <v>124172046</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,39 +909,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -949,13 +945,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562084</v>
+        <v>562174</v>
       </c>
       <c r="R4" t="n">
-        <v>6407227</v>
+        <v>6407304</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,6 +989,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1011,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124172370</v>
+        <v>124172550</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,49 +1020,53 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 16954, Vrå, Sm</t>
+          <t>A  16954, Vrå, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562074</v>
+        <v>562129</v>
       </c>
       <c r="R5" t="n">
-        <v>6407252</v>
+        <v>6407291</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,7 +1104,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124172454</v>
+        <v>124172562</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,35 +1134,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1170,13 +1174,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561985</v>
+        <v>562084</v>
       </c>
       <c r="R6" t="n">
-        <v>6407239</v>
+        <v>6407227</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,7 +1218,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1233,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124172498</v>
+        <v>124171893</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>57666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,29 +1252,33 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1281,13 +1288,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562127</v>
+        <v>562174</v>
       </c>
       <c r="R7" t="n">
-        <v>6407212</v>
+        <v>6407246</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1321,7 +1328,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Torrträd</t>
+          <t>Även sång</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,7 +1355,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124171931</v>
+        <v>124172481</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1396,10 +1403,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562188</v>
+        <v>562037</v>
       </c>
       <c r="R8" t="n">
-        <v>6407299</v>
+        <v>6407226</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124172266</v>
+        <v>124171837</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,35 +1478,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1507,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562099</v>
+        <v>562199</v>
       </c>
       <c r="R9" t="n">
-        <v>6407295</v>
+        <v>6407237</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,13 +1552,17 @@
           <t>2025-04-17</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Låga</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1570,7 +1581,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124172481</v>
+        <v>124172219</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1618,10 +1629,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562037</v>
+        <v>562109</v>
       </c>
       <c r="R10" t="n">
-        <v>6407226</v>
+        <v>6407282</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124172550</v>
+        <v>124172400</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1693,53 +1704,49 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A  16954, Vrå, Sm</t>
+          <t>A 16954, Vrå, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562129</v>
+        <v>562048</v>
       </c>
       <c r="R11" t="n">
-        <v>6407291</v>
+        <v>6407247</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1777,6 +1784,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1909,7 +1917,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124172016</v>
+        <v>124172266</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1957,10 +1965,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562185</v>
+        <v>562099</v>
       </c>
       <c r="R13" t="n">
-        <v>6407314</v>
+        <v>6407295</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124172046</v>
+        <v>124172498</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2032,35 +2040,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2068,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562174</v>
+        <v>562127</v>
       </c>
       <c r="R14" t="n">
-        <v>6407304</v>
+        <v>6407212</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2106,13 +2114,17 @@
           <t>2025-04-17</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Torrträd</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2131,10 +2143,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124171893</v>
+        <v>124172151</v>
       </c>
       <c r="B15" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2143,39 +2155,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2183,13 +2191,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562174</v>
+        <v>562104</v>
       </c>
       <c r="R15" t="n">
-        <v>6407246</v>
+        <v>6407296</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2221,17 +2229,13 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Även sång</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2250,10 +2254,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124171837</v>
+        <v>124172370</v>
       </c>
       <c r="B16" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2262,35 +2266,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2298,10 +2302,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562199</v>
+        <v>562074</v>
       </c>
       <c r="R16" t="n">
-        <v>6407237</v>
+        <v>6407252</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2336,17 +2340,13 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Låga</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2365,10 +2365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124172400</v>
+        <v>124172327</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2377,35 +2377,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2413,10 +2416,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562048</v>
+        <v>562106</v>
       </c>
       <c r="R17" t="n">
-        <v>6407247</v>
+        <v>6407323</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2476,10 +2479,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124172327</v>
+        <v>124172454</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2488,38 +2491,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562106</v>
+        <v>561985</v>
       </c>
       <c r="R18" t="n">
-        <v>6407323</v>
+        <v>6407239</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 16954-2025 artfynd.xlsx
+++ b/artfynd/A 16954-2025 artfynd.xlsx
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124172400</v>
+        <v>124172528</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,35 +1704,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1740,13 +1744,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562048</v>
+        <v>562104</v>
       </c>
       <c r="R11" t="n">
-        <v>6407247</v>
+        <v>6407251</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1784,7 +1788,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1803,10 +1806,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124172528</v>
+        <v>124172400</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1815,39 +1818,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1855,13 +1854,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562104</v>
+        <v>562048</v>
       </c>
       <c r="R12" t="n">
-        <v>6407251</v>
+        <v>6407247</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1899,6 +1898,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16954-2025 artfynd.xlsx
+++ b/artfynd/A 16954-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124171931</v>
+        <v>124172151</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562188</v>
+        <v>562104</v>
       </c>
       <c r="R2" t="n">
-        <v>6407299</v>
+        <v>6407296</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124172016</v>
+        <v>124172219</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562185</v>
+        <v>562109</v>
       </c>
       <c r="R3" t="n">
-        <v>6407314</v>
+        <v>6407282</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124172046</v>
+        <v>124172562</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,35 +909,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562174</v>
+        <v>562084</v>
       </c>
       <c r="R4" t="n">
-        <v>6407304</v>
+        <v>6407227</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +993,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1008,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124172550</v>
+        <v>124172528</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,20 +1023,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1050,20 +1053,20 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A  16954, Vrå, Sm</t>
+          <t>A 16954, Vrå, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562129</v>
+        <v>562104</v>
       </c>
       <c r="R5" t="n">
-        <v>6407291</v>
+        <v>6407251</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1122,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124172562</v>
+        <v>124172454</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,39 +1137,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1174,13 +1173,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562084</v>
+        <v>561985</v>
       </c>
       <c r="R6" t="n">
-        <v>6407227</v>
+        <v>6407239</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,6 +1217,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1236,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124171893</v>
+        <v>124172046</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,39 +1248,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1291,10 +1287,10 @@
         <v>562174</v>
       </c>
       <c r="R7" t="n">
-        <v>6407246</v>
+        <v>6407304</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1326,17 +1322,13 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Även sång</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1355,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124172481</v>
+        <v>124171837</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,35 +1359,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1403,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562037</v>
+        <v>562199</v>
       </c>
       <c r="R8" t="n">
-        <v>6407226</v>
+        <v>6407237</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,13 +1433,17 @@
           <t>2025-04-17</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Låga</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1466,10 +1462,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124171837</v>
+        <v>124172016</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,35 +1474,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1514,10 +1510,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562199</v>
+        <v>562185</v>
       </c>
       <c r="R9" t="n">
-        <v>6407237</v>
+        <v>6407314</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,17 +1548,13 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Låga</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1581,7 +1573,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124172219</v>
+        <v>124172370</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1629,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562109</v>
+        <v>562074</v>
       </c>
       <c r="R10" t="n">
-        <v>6407282</v>
+        <v>6407252</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,7 +1684,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124172528</v>
+        <v>124172498</v>
       </c>
       <c r="B11" t="n">
         <v>57529</v>
@@ -1725,16 +1717,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1744,13 +1732,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562104</v>
+        <v>562127</v>
       </c>
       <c r="R11" t="n">
-        <v>6407251</v>
+        <v>6407212</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1780,6 +1768,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Torrträd</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2028,10 +2021,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124172498</v>
+        <v>124172327</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2044,31 +2037,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2076,10 +2072,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562127</v>
+        <v>562106</v>
       </c>
       <c r="R14" t="n">
-        <v>6407212</v>
+        <v>6407323</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2114,17 +2110,13 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Torrträd</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2143,10 +2135,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124172151</v>
+        <v>124171893</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2155,35 +2147,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2191,13 +2187,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562104</v>
+        <v>562174</v>
       </c>
       <c r="R15" t="n">
-        <v>6407296</v>
+        <v>6407246</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2229,13 +2225,17 @@
           <t>2025-04-17</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Även sång</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2254,10 +2254,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124172370</v>
+        <v>124172550</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2266,49 +2266,53 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A 16954, Vrå, Sm</t>
+          <t>A  16954, Vrå, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562074</v>
+        <v>562129</v>
       </c>
       <c r="R16" t="n">
-        <v>6407252</v>
+        <v>6407291</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2346,7 +2350,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2365,10 +2368,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124172327</v>
+        <v>124171931</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2377,38 +2380,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562106</v>
+        <v>562188</v>
       </c>
       <c r="R17" t="n">
-        <v>6407323</v>
+        <v>6407299</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2479,7 +2479,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124172454</v>
+        <v>124172481</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>561985</v>
+        <v>562037</v>
       </c>
       <c r="R18" t="n">
-        <v>6407239</v>
+        <v>6407226</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 16954-2025 artfynd.xlsx
+++ b/artfynd/A 16954-2025 artfynd.xlsx
@@ -2021,10 +2021,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124172327</v>
+        <v>124171893</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>57666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2037,34 +2037,35 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2072,13 +2073,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562106</v>
+        <v>562174</v>
       </c>
       <c r="R14" t="n">
-        <v>6407323</v>
+        <v>6407246</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2110,13 +2111,17 @@
           <t>2025-04-17</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Även sång</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2135,10 +2140,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124171893</v>
+        <v>124172327</v>
       </c>
       <c r="B15" t="n">
-        <v>57666</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2151,35 +2156,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2187,13 +2191,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562174</v>
+        <v>562106</v>
       </c>
       <c r="R15" t="n">
-        <v>6407246</v>
+        <v>6407323</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2225,17 +2229,13 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Även sång</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16954-2025 artfynd.xlsx
+++ b/artfynd/A 16954-2025 artfynd.xlsx
@@ -675,47 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124172151</v>
+        <v>124172327</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562104</v>
+        <v>562106</v>
       </c>
       <c r="R2" t="n">
-        <v>6407296</v>
+        <v>6407323</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,47 +784,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124172219</v>
+        <v>124171837</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562109</v>
+        <v>562199</v>
       </c>
       <c r="R3" t="n">
-        <v>6407282</v>
+        <v>6407237</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,13 +865,17 @@
           <t>2025-04-17</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Låga</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,15 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124172562</v>
+        <v>124172498</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,16 +905,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -930,16 +922,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -949,13 +937,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562084</v>
+        <v>562127</v>
       </c>
       <c r="R4" t="n">
-        <v>6407227</v>
+        <v>6407212</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,6 +973,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Torrträd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,16 +1007,11 @@
         <v>124172528</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1125,61 +1113,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124172454</v>
+        <v>124172550</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 16954, Vrå, Sm</t>
+          <t>A  16954, Vrå, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561985</v>
+        <v>562129</v>
       </c>
       <c r="R6" t="n">
-        <v>6407239</v>
+        <v>6407291</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1217,7 +1204,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1236,47 +1222,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124172046</v>
+        <v>124172562</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1284,13 +1269,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562174</v>
+        <v>562084</v>
       </c>
       <c r="R7" t="n">
-        <v>6407304</v>
+        <v>6407227</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,7 +1313,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1347,15 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124171837</v>
+        <v>124171893</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,29 +1342,33 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1395,13 +1378,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562199</v>
+        <v>562174</v>
       </c>
       <c r="R8" t="n">
-        <v>6407237</v>
+        <v>6407246</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1435,7 +1418,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Låga</t>
+          <t>Även sång</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,15 +1445,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124172016</v>
+        <v>124171931</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562185</v>
+        <v>562188</v>
       </c>
       <c r="R9" t="n">
-        <v>6407314</v>
+        <v>6407299</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,15 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124172370</v>
+        <v>124172016</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,10 +1594,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562074</v>
+        <v>562185</v>
       </c>
       <c r="R10" t="n">
-        <v>6407252</v>
+        <v>6407314</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,47 +1657,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124172498</v>
+        <v>124172046</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1732,10 +1700,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562127</v>
+        <v>562174</v>
       </c>
       <c r="R11" t="n">
-        <v>6407212</v>
+        <v>6407304</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,17 +1738,13 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Torrträd</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1799,15 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124172400</v>
+        <v>124172151</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562048</v>
+        <v>562104</v>
       </c>
       <c r="R12" t="n">
-        <v>6407247</v>
+        <v>6407296</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,15 +1869,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124172266</v>
+        <v>124172219</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562099</v>
+        <v>562109</v>
       </c>
       <c r="R13" t="n">
-        <v>6407295</v>
+        <v>6407282</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,51 +1975,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124171893</v>
+        <v>124172266</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2073,13 +2018,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562174</v>
+        <v>562099</v>
       </c>
       <c r="R14" t="n">
-        <v>6407246</v>
+        <v>6407295</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2111,17 +2056,13 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Även sång</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2140,50 +2081,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124172327</v>
+        <v>124172370</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2191,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562106</v>
+        <v>562074</v>
       </c>
       <c r="R15" t="n">
-        <v>6407323</v>
+        <v>6407252</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2254,65 +2187,56 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124172550</v>
+        <v>124172400</v>
       </c>
       <c r="B16" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A  16954, Vrå, Sm</t>
+          <t>A 16954, Vrå, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562129</v>
+        <v>562048</v>
       </c>
       <c r="R16" t="n">
-        <v>6407291</v>
+        <v>6407247</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2350,6 +2274,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2368,15 +2293,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124171931</v>
+        <v>124172454</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2416,10 +2336,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562188</v>
+        <v>561985</v>
       </c>
       <c r="R17" t="n">
-        <v>6407299</v>
+        <v>6407239</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2482,12 +2402,7 @@
         <v>124172481</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 16954-2025 artfynd.xlsx
+++ b/artfynd/A 16954-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124172327</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124171837</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124172498</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,6 +1130,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124172528</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1219,6 +1244,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124172550</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1328,6 +1358,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124172562</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,6 +1477,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124171893</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1548,6 +1588,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124171931</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1654,6 +1699,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124172016</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1760,6 +1810,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124172046</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1866,6 +1921,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124172151</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1972,6 +2032,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124172219</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2078,6 +2143,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124172266</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2184,6 +2254,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124172370</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2290,6 +2365,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124172400</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2396,6 +2476,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124172454</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2502,8 +2587,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124172481</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>